--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.33768207331998</v>
+        <v>6.717373336914497</v>
       </c>
       <c r="D2" t="n">
-        <v>41.45165298169213</v>
+        <v>6.735893609524972</v>
       </c>
       <c r="E2" t="n">
-        <v>14.90962391480993</v>
+        <v>2.422813886156613</v>
       </c>
       <c r="F2" t="n">
-        <v>14.89387744682781</v>
+        <v>2.420255085109519</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.51843424370013</v>
+        <v>1.871745564601271</v>
       </c>
       <c r="D3" t="n">
-        <v>11.66389808803651</v>
+        <v>1.895383439305933</v>
       </c>
       <c r="E3" t="n">
-        <v>14.90962391480993</v>
+        <v>2.422813886156613</v>
       </c>
       <c r="F3" t="n">
-        <v>14.89387744682781</v>
+        <v>2.420255085109519</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
